--- a/files/teaching/AGB_Student_Eval_Data.xlsx
+++ b/files/teaching/AGB_Student_Eval_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agben\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benson\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1BCAB37-68E1-4BE1-BF35-08EBB0678B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E2E0E0-AD67-43F3-94DE-6BB9442ADD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="6" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="96">
   <si>
     <t>Course Title</t>
   </si>
@@ -236,9 +236,6 @@
     <t xml:space="preserve">PDF copies of the evaluations can be found here: </t>
   </si>
   <si>
-    <t>https://sites.uci.edu/agbenson/teaching/</t>
-  </si>
-  <si>
     <t>Course</t>
   </si>
   <si>
@@ -378,6 +375,9 @@
   <si>
     <t>Disclaimer: In AY 20-21, the set of responses availabile for this question excluded "Excellent." I taught once course in AY 20-21, which is excluded from the summary presented here due to the inconsistency.</t>
   </si>
+  <si>
+    <t>https://a-g-benson.github.io/teaching.html</t>
+  </si>
 </sst>
 </file>
 
@@ -454,7 +454,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -493,6 +493,10 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -508,10 +512,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1123,16 +1124,16 @@
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>29</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>110</c:v>
+                  <c:v>112</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>92</c:v>
+                  <c:v>95</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>94</c:v>
+                  <c:v>105</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>116</c:v>
@@ -1168,6 +1169,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1175,7 +1177,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1474,6 +1475,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1481,7 +1483,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1788,6 +1789,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1795,7 +1797,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3614,10 +3615,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3886,7 +3883,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -3894,34 +3891,34 @@
         <v>61</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I5">
-        <f>SUM('Raw Data'!E3:E16)</f>
-        <v>483</v>
+        <f>SUM('Raw Data'!E3:E17)</f>
+        <v>502</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -3944,7 +3941,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -3969,17 +3966,17 @@
         <v>56</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -4010,141 +4007,141 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5">
         <f>SUM(C5:J5)</f>
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="C5">
-        <f>SUM('Collapsed Data'!BI2:BI13)</f>
+        <f>SUM('Collapsed Data'!BI3:BI13)</f>
         <v>30</v>
       </c>
       <c r="D5">
-        <f>SUM('Collapsed Data'!BJ2:BJ13)</f>
-        <v>20</v>
+        <f>SUM('Collapsed Data'!BJ3:BJ13)</f>
+        <v>19</v>
       </c>
       <c r="E5">
-        <f>SUM('Collapsed Data'!BK2:BK13)</f>
-        <v>28</v>
+        <f>SUM('Collapsed Data'!BK3:BK13)</f>
+        <v>26</v>
       </c>
       <c r="F5">
-        <f>SUM('Collapsed Data'!BL2:BL13)</f>
-        <v>26</v>
+        <f>SUM('Collapsed Data'!BL3:BL13)</f>
+        <v>23</v>
       </c>
       <c r="G5">
-        <f>SUM('Collapsed Data'!BM2:BM13)</f>
-        <v>94</v>
+        <f>SUM('Collapsed Data'!BM3:BM13)</f>
+        <v>90</v>
       </c>
       <c r="H5">
-        <f>SUM('Collapsed Data'!BN2:BN13)</f>
-        <v>70</v>
+        <f>SUM('Collapsed Data'!BN3:BN13)</f>
+        <v>65</v>
       </c>
       <c r="I5">
-        <f>SUM('Collapsed Data'!BO2:BO13)</f>
-        <v>87</v>
+        <f>SUM('Collapsed Data'!BO3:BO13)</f>
+        <v>81</v>
       </c>
       <c r="J5">
-        <f>SUM('Collapsed Data'!BP2:BP13)</f>
-        <v>157</v>
+        <f>SUM('Collapsed Data'!BP3:BP13)</f>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
-        <v>69</v>
+      <c r="A6" s="24" t="s">
+        <v>68</v>
       </c>
       <c r="B6" s="10">
         <f>B5-C5</f>
-        <v>482</v>
+        <v>454</v>
       </c>
       <c r="D6" s="9">
         <f t="shared" ref="D6:J6" si="0">D5/$B$6</f>
-        <v>4.1493775933609957E-2</v>
+        <v>4.185022026431718E-2</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>5.8091286307053944E-2</v>
+        <v>5.7268722466960353E-2</v>
       </c>
       <c r="F6" s="9">
         <f t="shared" si="0"/>
-        <v>5.3941908713692949E-2</v>
+        <v>5.0660792951541848E-2</v>
       </c>
       <c r="G6" s="9">
         <f t="shared" si="0"/>
-        <v>0.19502074688796681</v>
+        <v>0.19823788546255505</v>
       </c>
       <c r="H6" s="9">
         <f t="shared" si="0"/>
-        <v>0.14522821576763487</v>
+        <v>0.14317180616740088</v>
       </c>
       <c r="I6" s="9">
         <f t="shared" si="0"/>
-        <v>0.18049792531120332</v>
+        <v>0.17841409691629956</v>
       </c>
       <c r="J6" s="9">
         <f t="shared" si="0"/>
-        <v>0.32572614107883818</v>
+        <v>0.33039647577092512</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="20"/>
+      <c r="A7" s="22"/>
       <c r="D7" s="13">
         <f>D5*(D4-$D$10)^2</f>
-        <v>350.92035261100881</v>
+        <v>335.23031205728819</v>
       </c>
       <c r="E7" s="13">
         <f t="shared" ref="E7:J7" si="1">E5*(E4-$D$10)^2</f>
-        <v>284.71587954752846</v>
+        <v>266.31330901046022</v>
       </c>
       <c r="F7" s="13">
         <f t="shared" si="1"/>
-        <v>124.56160362252719</v>
+        <v>111.36458596130338</v>
       </c>
       <c r="G7" s="13">
         <f t="shared" si="1"/>
-        <v>132.84432947091136</v>
+        <v>129.69517165091509</v>
       </c>
       <c r="H7" s="13">
         <f t="shared" si="1"/>
-        <v>2.4950930596925041</v>
+        <v>2.6114663587494511</v>
       </c>
       <c r="I7" s="13">
         <f t="shared" si="1"/>
-        <v>57.250421824693063</v>
+        <v>51.782923208290434</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="1"/>
-        <v>515.03182193832731</v>
+        <v>485.76214364726644</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="14" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="C10" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10" s="16">
         <f>SUMPRODUCT(D4:J4,D6:J6)</f>
-        <v>5.1887966804979255</v>
+        <v>5.2004405286343616</v>
       </c>
       <c r="J10" s="17"/>
     </row>
     <row r="11" spans="1:10" s="14" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="C11" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D11" s="16">
         <f>SQRT(SUM(D7:J7)/(B6-1))</f>
-        <v>1.7468828799931249</v>
+        <v>1.747126250913754</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="14" customFormat="1" ht="65.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
+      <c r="A12" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
       <c r="D12" s="19">
         <f>SUM(H6:J6)</f>
-        <v>0.65145228215767637</v>
+        <v>0.65198237885462551</v>
       </c>
     </row>
   </sheetData>
@@ -4169,7 +4166,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -4194,17 +4191,17 @@
         <v>56</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -4235,141 +4232,141 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5">
         <f>SUM(C5:J5)</f>
-        <v>508</v>
+        <v>480</v>
       </c>
       <c r="C5">
-        <f>SUM('Collapsed Data'!BQ2:BQ13)</f>
+        <f>SUM('Collapsed Data'!BQ3:BQ13)</f>
         <v>25</v>
       </c>
       <c r="D5">
-        <f>SUM('Collapsed Data'!BR2:BR13)</f>
+        <f>SUM('Collapsed Data'!BR3:BR13)</f>
+        <v>21</v>
+      </c>
+      <c r="E5">
+        <f>SUM('Collapsed Data'!BS3:BS13)</f>
+        <v>19</v>
+      </c>
+      <c r="F5">
+        <f>SUM('Collapsed Data'!BT3:BT13)</f>
         <v>22</v>
       </c>
-      <c r="E5">
-        <f>SUM('Collapsed Data'!BS2:BS13)</f>
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <f>SUM('Collapsed Data'!BT2:BT13)</f>
-        <v>25</v>
-      </c>
       <c r="G5">
-        <f>SUM('Collapsed Data'!BU2:BU13)</f>
-        <v>101</v>
+        <f>SUM('Collapsed Data'!BU3:BU13)</f>
+        <v>97</v>
       </c>
       <c r="H5">
-        <f>SUM('Collapsed Data'!BV2:BV13)</f>
-        <v>62</v>
+        <f>SUM('Collapsed Data'!BV3:BV13)</f>
+        <v>57</v>
       </c>
       <c r="I5">
-        <f>SUM('Collapsed Data'!BW2:BW13)</f>
-        <v>90</v>
+        <f>SUM('Collapsed Data'!BW3:BW13)</f>
+        <v>84</v>
       </c>
       <c r="J5">
-        <f>SUM('Collapsed Data'!BX2:BX13)</f>
-        <v>162</v>
+        <f>SUM('Collapsed Data'!BX3:BX13)</f>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
-        <v>69</v>
+      <c r="A6" s="24" t="s">
+        <v>68</v>
       </c>
       <c r="B6" s="10">
         <f>B5-C5</f>
-        <v>483</v>
+        <v>455</v>
       </c>
       <c r="D6" s="9">
         <f t="shared" ref="D6:J6" si="0">D5/$B$6</f>
-        <v>4.5548654244306416E-2</v>
+        <v>4.6153846153846156E-2</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>4.3478260869565216E-2</v>
+        <v>4.1758241758241756E-2</v>
       </c>
       <c r="F6" s="9">
         <f t="shared" si="0"/>
-        <v>5.1759834368530024E-2</v>
+        <v>4.8351648351648353E-2</v>
       </c>
       <c r="G6" s="9">
         <f t="shared" si="0"/>
-        <v>0.20910973084886128</v>
+        <v>0.21318681318681318</v>
       </c>
       <c r="H6" s="9">
         <f t="shared" si="0"/>
-        <v>0.12836438923395446</v>
+        <v>0.12527472527472527</v>
       </c>
       <c r="I6" s="9">
         <f t="shared" si="0"/>
-        <v>0.18633540372670807</v>
+        <v>0.18461538461538463</v>
       </c>
       <c r="J6" s="9">
         <f t="shared" si="0"/>
-        <v>0.33540372670807456</v>
+        <v>0.34065934065934067</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="20"/>
+      <c r="A7" s="22"/>
       <c r="D7" s="13">
         <f>D5*(D4-$D$10)^2</f>
-        <v>393.99453896240283</v>
+        <v>378.62627218934915</v>
       </c>
       <c r="E7" s="13">
         <f t="shared" ref="E7:J7" si="1">E5*(E4-$D$10)^2</f>
-        <v>219.34656584751104</v>
+        <v>200.21278106508876</v>
       </c>
       <c r="F7" s="13">
         <f t="shared" si="1"/>
-        <v>124.5326612056291</v>
+        <v>110.99455621301774</v>
       </c>
       <c r="G7" s="13">
         <f t="shared" si="1"/>
-        <v>153.27137156059655</v>
+        <v>150.63124260355031</v>
       </c>
       <c r="H7" s="13">
         <f t="shared" si="1"/>
-        <v>3.3337534131485023</v>
+        <v>3.453727810650888</v>
       </c>
       <c r="I7" s="13">
         <f t="shared" si="1"/>
-        <v>53.100189035916806</v>
+        <v>47.735857988165684</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="1"/>
-        <v>506.44990548204146</v>
+        <v>476.7763313609467</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="14" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="C10" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10" s="16">
         <f>SUMPRODUCT(D4:J4,D6:J6)</f>
-        <v>5.2318840579710146</v>
+        <v>5.2461538461538462</v>
       </c>
       <c r="J10" s="17"/>
     </row>
     <row r="11" spans="1:10" s="14" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="C11" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D11" s="16">
         <f>SQRT(SUM(D7:J7)/(B6-1))</f>
-        <v>1.7368527992551914</v>
+        <v>1.7361349860928483</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="14" customFormat="1" ht="65.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
+      <c r="A12" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
       <c r="D12" s="19">
         <f>SUM(H6:J6)</f>
-        <v>0.65010351966873703</v>
+        <v>0.65054945054945057</v>
       </c>
     </row>
   </sheetData>
@@ -4403,105 +4400,105 @@
   <sheetData>
     <row r="1" spans="1:84" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F1" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="20" t="s">
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
+      <c r="R1" s="24"/>
+      <c r="S1" s="24"/>
+      <c r="T1" s="24"/>
+      <c r="U1" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="20"/>
-      <c r="Z1" s="20"/>
-      <c r="AA1" s="20"/>
-      <c r="AB1" s="20"/>
-      <c r="AC1" s="20" t="s">
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="AD1" s="20"/>
-      <c r="AE1" s="20"/>
-      <c r="AF1" s="20"/>
-      <c r="AG1" s="20"/>
-      <c r="AH1" s="20"/>
-      <c r="AI1" s="20"/>
-      <c r="AJ1" s="20"/>
-      <c r="AK1" s="20" t="s">
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="22"/>
+      <c r="AF1" s="22"/>
+      <c r="AG1" s="22"/>
+      <c r="AH1" s="22"/>
+      <c r="AI1" s="22"/>
+      <c r="AJ1" s="22"/>
+      <c r="AK1" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="AL1" s="20"/>
-      <c r="AM1" s="20"/>
-      <c r="AN1" s="20"/>
-      <c r="AO1" s="20"/>
-      <c r="AP1" s="20"/>
-      <c r="AQ1" s="20"/>
-      <c r="AR1" s="20"/>
-      <c r="AS1" s="20" t="s">
+      <c r="AL1" s="22"/>
+      <c r="AM1" s="22"/>
+      <c r="AN1" s="22"/>
+      <c r="AO1" s="22"/>
+      <c r="AP1" s="22"/>
+      <c r="AQ1" s="22"/>
+      <c r="AR1" s="22"/>
+      <c r="AS1" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="AT1" s="20"/>
-      <c r="AU1" s="20"/>
-      <c r="AV1" s="20"/>
-      <c r="AW1" s="20"/>
-      <c r="AX1" s="20"/>
-      <c r="AY1" s="20"/>
-      <c r="AZ1" s="20"/>
-      <c r="BA1" s="20" t="s">
+      <c r="AT1" s="22"/>
+      <c r="AU1" s="22"/>
+      <c r="AV1" s="22"/>
+      <c r="AW1" s="22"/>
+      <c r="AX1" s="22"/>
+      <c r="AY1" s="22"/>
+      <c r="AZ1" s="22"/>
+      <c r="BA1" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="BB1" s="20"/>
-      <c r="BC1" s="20"/>
-      <c r="BD1" s="20"/>
-      <c r="BE1" s="20"/>
-      <c r="BF1" s="20"/>
-      <c r="BG1" s="20"/>
-      <c r="BH1" s="20"/>
-      <c r="BI1" s="20" t="s">
+      <c r="BB1" s="22"/>
+      <c r="BC1" s="22"/>
+      <c r="BD1" s="22"/>
+      <c r="BE1" s="22"/>
+      <c r="BF1" s="22"/>
+      <c r="BG1" s="22"/>
+      <c r="BH1" s="22"/>
+      <c r="BI1" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="BJ1" s="20"/>
-      <c r="BK1" s="20"/>
-      <c r="BL1" s="20"/>
-      <c r="BM1" s="20"/>
-      <c r="BN1" s="20"/>
-      <c r="BO1" s="20"/>
-      <c r="BP1" s="20"/>
-      <c r="BQ1" s="20" t="s">
+      <c r="BJ1" s="22"/>
+      <c r="BK1" s="22"/>
+      <c r="BL1" s="22"/>
+      <c r="BM1" s="22"/>
+      <c r="BN1" s="22"/>
+      <c r="BO1" s="22"/>
+      <c r="BP1" s="22"/>
+      <c r="BQ1" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="BR1" s="20"/>
-      <c r="BS1" s="20"/>
-      <c r="BT1" s="20"/>
-      <c r="BU1" s="20"/>
-      <c r="BV1" s="20"/>
-      <c r="BW1" s="20"/>
-      <c r="BX1" s="20"/>
-      <c r="BY1" s="21" t="s">
+      <c r="BR1" s="22"/>
+      <c r="BS1" s="22"/>
+      <c r="BT1" s="22"/>
+      <c r="BU1" s="22"/>
+      <c r="BV1" s="22"/>
+      <c r="BW1" s="22"/>
+      <c r="BX1" s="22"/>
+      <c r="BY1" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="BZ1" s="21"/>
-      <c r="CA1" s="21"/>
-      <c r="CB1" s="21"/>
-      <c r="CC1" s="21"/>
-      <c r="CD1" s="21"/>
-      <c r="CE1" s="21"/>
+      <c r="BZ1" s="23"/>
+      <c r="CA1" s="23"/>
+      <c r="CB1" s="23"/>
+      <c r="CC1" s="23"/>
+      <c r="CD1" s="23"/>
+      <c r="CE1" s="23"/>
       <c r="CF1" s="2"/>
     </row>
     <row r="2" spans="1:84" x14ac:dyDescent="0.25">
@@ -8277,7 +8274,7 @@
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>8</v>
@@ -8517,7 +8514,7 @@
         <v>11</v>
       </c>
       <c r="CE17" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -8562,103 +8559,103 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:84" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="22" t="s">
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="20" t="s">
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
+      <c r="R1" s="24"/>
+      <c r="S1" s="24"/>
+      <c r="T1" s="24"/>
+      <c r="U1" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="20"/>
-      <c r="Z1" s="20"/>
-      <c r="AA1" s="20"/>
-      <c r="AB1" s="20"/>
-      <c r="AC1" s="20" t="s">
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="AD1" s="20"/>
-      <c r="AE1" s="20"/>
-      <c r="AF1" s="20"/>
-      <c r="AG1" s="20"/>
-      <c r="AH1" s="20"/>
-      <c r="AI1" s="20"/>
-      <c r="AJ1" s="20"/>
-      <c r="AK1" s="20" t="s">
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="22"/>
+      <c r="AF1" s="22"/>
+      <c r="AG1" s="22"/>
+      <c r="AH1" s="22"/>
+      <c r="AI1" s="22"/>
+      <c r="AJ1" s="22"/>
+      <c r="AK1" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="AL1" s="20"/>
-      <c r="AM1" s="20"/>
-      <c r="AN1" s="20"/>
-      <c r="AO1" s="20"/>
-      <c r="AP1" s="20"/>
-      <c r="AQ1" s="20"/>
-      <c r="AR1" s="20"/>
-      <c r="AS1" s="20" t="s">
+      <c r="AL1" s="22"/>
+      <c r="AM1" s="22"/>
+      <c r="AN1" s="22"/>
+      <c r="AO1" s="22"/>
+      <c r="AP1" s="22"/>
+      <c r="AQ1" s="22"/>
+      <c r="AR1" s="22"/>
+      <c r="AS1" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="AT1" s="20"/>
-      <c r="AU1" s="20"/>
-      <c r="AV1" s="20"/>
-      <c r="AW1" s="20"/>
-      <c r="AX1" s="20"/>
-      <c r="AY1" s="20"/>
-      <c r="AZ1" s="20"/>
-      <c r="BA1" s="20" t="s">
+      <c r="AT1" s="22"/>
+      <c r="AU1" s="22"/>
+      <c r="AV1" s="22"/>
+      <c r="AW1" s="22"/>
+      <c r="AX1" s="22"/>
+      <c r="AY1" s="22"/>
+      <c r="AZ1" s="22"/>
+      <c r="BA1" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="BB1" s="20"/>
-      <c r="BC1" s="20"/>
-      <c r="BD1" s="20"/>
-      <c r="BE1" s="20"/>
-      <c r="BF1" s="20"/>
-      <c r="BG1" s="20"/>
-      <c r="BH1" s="20"/>
-      <c r="BI1" s="20" t="s">
+      <c r="BB1" s="22"/>
+      <c r="BC1" s="22"/>
+      <c r="BD1" s="22"/>
+      <c r="BE1" s="22"/>
+      <c r="BF1" s="22"/>
+      <c r="BG1" s="22"/>
+      <c r="BH1" s="22"/>
+      <c r="BI1" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="BJ1" s="20"/>
-      <c r="BK1" s="20"/>
-      <c r="BL1" s="20"/>
-      <c r="BM1" s="20"/>
-      <c r="BN1" s="20"/>
-      <c r="BO1" s="20"/>
-      <c r="BP1" s="20"/>
-      <c r="BQ1" s="20" t="s">
+      <c r="BJ1" s="22"/>
+      <c r="BK1" s="22"/>
+      <c r="BL1" s="22"/>
+      <c r="BM1" s="22"/>
+      <c r="BN1" s="22"/>
+      <c r="BO1" s="22"/>
+      <c r="BP1" s="22"/>
+      <c r="BQ1" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="BR1" s="20"/>
-      <c r="BS1" s="20"/>
-      <c r="BT1" s="20"/>
-      <c r="BU1" s="20"/>
-      <c r="BV1" s="20"/>
-      <c r="BW1" s="20"/>
-      <c r="BX1" s="20"/>
-      <c r="BY1" s="21" t="s">
+      <c r="BR1" s="22"/>
+      <c r="BS1" s="22"/>
+      <c r="BT1" s="22"/>
+      <c r="BU1" s="22"/>
+      <c r="BV1" s="22"/>
+      <c r="BW1" s="22"/>
+      <c r="BX1" s="22"/>
+      <c r="BY1" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="BZ1" s="21"/>
-      <c r="CA1" s="21"/>
-      <c r="CB1" s="21"/>
-      <c r="CC1" s="21"/>
-      <c r="CD1" s="21"/>
-      <c r="CE1" s="21"/>
+      <c r="BZ1" s="23"/>
+      <c r="CA1" s="23"/>
+      <c r="CB1" s="23"/>
+      <c r="CC1" s="23"/>
+      <c r="CD1" s="23"/>
+      <c r="CE1" s="23"/>
       <c r="CF1" s="2"/>
     </row>
     <row r="2" spans="1:84" x14ac:dyDescent="0.25">
@@ -12208,7 +12205,7 @@
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>8</v>
@@ -12523,8 +12520,8 @@
         <f>SUMIFS('Raw Data'!CD$3:CD$17,'Raw Data'!$B$3:$B$17,'Collapsed Data'!$B13,'Raw Data'!$C$3:$C$17,'Collapsed Data'!$C13)</f>
         <v>11</v>
       </c>
-      <c r="CE13" s="25" t="s">
-        <v>92</v>
+      <c r="CE13" s="20">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -12580,7 +12577,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I3" s="3"/>
     </row>
@@ -12616,74 +12613,74 @@
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>SUM(B6:H6)</f>
-        <v>459</v>
+        <v>476</v>
       </c>
       <c r="B6">
-        <f>SUM('Collapsed Data'!BY3:BY12)</f>
+        <f>SUM('Collapsed Data'!BY3:BY13)</f>
         <v>9</v>
       </c>
       <c r="C6">
-        <f>SUM('Collapsed Data'!BZ3:BZ12)</f>
+        <f>SUM('Collapsed Data'!BZ3:BZ13)</f>
         <v>9</v>
       </c>
       <c r="D6">
-        <f>SUM('Collapsed Data'!CA3:CA12)</f>
-        <v>29</v>
+        <f>SUM('Collapsed Data'!CA3:CA13)</f>
+        <v>30</v>
       </c>
       <c r="E6">
-        <f>SUM('Collapsed Data'!CB3:CB12)</f>
-        <v>110</v>
+        <f>SUM('Collapsed Data'!CB3:CB13)</f>
+        <v>112</v>
       </c>
       <c r="F6">
-        <f>SUM('Collapsed Data'!CC3:CC12)</f>
+        <f>SUM('Collapsed Data'!CC3:CC13)</f>
+        <v>95</v>
+      </c>
+      <c r="G6">
+        <f>SUM('Collapsed Data'!CD3:CD13)</f>
+        <v>105</v>
+      </c>
+      <c r="H6">
+        <f>SUM('Collapsed Data'!CE3:CE13)</f>
+        <v>116</v>
+      </c>
+      <c r="J6" s="21" t="s">
         <v>92</v>
-      </c>
-      <c r="G6">
-        <f>SUM('Collapsed Data'!CD3:CD12)</f>
-        <v>94</v>
-      </c>
-      <c r="H6">
-        <f>SUM('Collapsed Data'!CE3:CE12)</f>
-        <v>116</v>
-      </c>
-      <c r="J6" s="26" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="5">
         <f t="shared" ref="B7:H7" si="0">B6/$A$6</f>
-        <v>1.9607843137254902E-2</v>
+        <v>1.8907563025210083E-2</v>
       </c>
       <c r="C7" s="5">
         <f t="shared" si="0"/>
-        <v>1.9607843137254902E-2</v>
+        <v>1.8907563025210083E-2</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="0"/>
-        <v>6.3180827886710242E-2</v>
+        <v>6.3025210084033612E-2</v>
       </c>
       <c r="E7" s="5">
         <f t="shared" si="0"/>
-        <v>0.23965141612200436</v>
+        <v>0.23529411764705882</v>
       </c>
       <c r="F7" s="5">
         <f t="shared" si="0"/>
-        <v>0.20043572984749455</v>
+        <v>0.19957983193277312</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" si="0"/>
-        <v>0.20479302832244009</v>
+        <v>0.22058823529411764</v>
       </c>
       <c r="H7" s="5">
         <f t="shared" si="0"/>
-        <v>0.25272331154684097</v>
+        <v>0.24369747899159663</v>
       </c>
       <c r="I7" s="5"/>
-      <c r="J7" s="5">
+      <c r="J7" s="27">
         <f>SUM(E7:H7)</f>
-        <v>0.89760348583878002</v>
+        <v>0.89915966386554624</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -12692,34 +12689,34 @@
       <c r="H9" s="7"/>
     </row>
     <row r="37" spans="3:9" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C37" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
+      <c r="C37" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
     </row>
     <row r="38" spans="3:9" x14ac:dyDescent="0.25">
       <c r="D38" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="3:9" x14ac:dyDescent="0.25">
@@ -12914,7 +12911,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -12939,17 +12936,17 @@
         <v>56</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -12980,141 +12977,141 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5">
         <f>SUM(C5:J5)</f>
-        <v>514</v>
+        <v>486</v>
       </c>
       <c r="C5">
-        <f>SUM('Collapsed Data'!U2:U13)</f>
+        <f>SUM('Collapsed Data'!U3:U13)</f>
         <v>15</v>
       </c>
       <c r="D5">
-        <f>SUM('Collapsed Data'!V2:V13)</f>
-        <v>12</v>
+        <f>SUM('Collapsed Data'!V3:V13)</f>
+        <v>11</v>
       </c>
       <c r="E5">
-        <f>SUM('Collapsed Data'!W2:W13)</f>
-        <v>16</v>
+        <f>SUM('Collapsed Data'!W3:W13)</f>
+        <v>14</v>
       </c>
       <c r="F5">
-        <f>SUM('Collapsed Data'!X2:X13)</f>
-        <v>33</v>
+        <f>SUM('Collapsed Data'!X3:X13)</f>
+        <v>30</v>
       </c>
       <c r="G5">
-        <f>SUM('Collapsed Data'!Y2:Y13)</f>
-        <v>100</v>
+        <f>SUM('Collapsed Data'!Y3:Y13)</f>
+        <v>96</v>
       </c>
       <c r="H5">
-        <f>SUM('Collapsed Data'!Z2:Z13)</f>
-        <v>73</v>
+        <f>SUM('Collapsed Data'!Z3:Z13)</f>
+        <v>68</v>
       </c>
       <c r="I5">
-        <f>SUM('Collapsed Data'!AA2:AA13)</f>
-        <v>105</v>
+        <f>SUM('Collapsed Data'!AA3:AA13)</f>
+        <v>99</v>
       </c>
       <c r="J5">
-        <f>SUM('Collapsed Data'!AB2:AB13)</f>
-        <v>160</v>
+        <f>SUM('Collapsed Data'!AB3:AB13)</f>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
-        <v>69</v>
+      <c r="A6" s="24" t="s">
+        <v>68</v>
       </c>
       <c r="B6" s="10">
         <f>B5-C5</f>
-        <v>499</v>
+        <v>471</v>
       </c>
       <c r="D6" s="9">
         <f t="shared" ref="D6:J6" si="0">D5/$B$6</f>
-        <v>2.4048096192384769E-2</v>
+        <v>2.3354564755838639E-2</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>3.2064128256513023E-2</v>
+        <v>2.9723991507430998E-2</v>
       </c>
       <c r="F6" s="9">
         <f t="shared" si="0"/>
-        <v>6.6132264529058113E-2</v>
+        <v>6.3694267515923567E-2</v>
       </c>
       <c r="G6" s="9">
         <f t="shared" si="0"/>
-        <v>0.20040080160320642</v>
+        <v>0.20382165605095542</v>
       </c>
       <c r="H6" s="9">
         <f t="shared" si="0"/>
-        <v>0.14629258517034069</v>
+        <v>0.14437367303609341</v>
       </c>
       <c r="I6" s="9">
         <f t="shared" si="0"/>
-        <v>0.21042084168336672</v>
+        <v>0.21019108280254778</v>
       </c>
       <c r="J6" s="9">
         <f t="shared" si="0"/>
-        <v>0.32064128256513025</v>
+        <v>0.32484076433121017</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="20"/>
+      <c r="A7" s="22"/>
       <c r="D7" s="13">
         <f>D5*(D4-$D$10)^2</f>
-        <v>224.63914602752595</v>
+        <v>207.77177798513341</v>
       </c>
       <c r="E7" s="13">
         <f t="shared" ref="E7:J7" si="1">E5*(E4-$D$10)^2</f>
-        <v>177.06595555841133</v>
+        <v>156.74678711329278</v>
       </c>
       <c r="F7" s="13">
         <f t="shared" si="1"/>
-        <v>178.63941510275049</v>
+        <v>165.12164117543637</v>
       </c>
       <c r="G7" s="13">
         <f t="shared" si="1"/>
-        <v>176.00089959478055</v>
+        <v>173.94339188878502</v>
       </c>
       <c r="H7" s="13">
         <f t="shared" si="1"/>
-        <v>7.789273938658849</v>
+        <v>8.144085178123035</v>
       </c>
       <c r="I7" s="13">
         <f t="shared" si="1"/>
-        <v>47.606555796964763</v>
+        <v>42.334536898048697</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="1"/>
-        <v>448.01426500295213</v>
+        <v>418.5280133068282</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="14" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="C10" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10" s="16">
         <f>SUMPRODUCT(D4:J4,D6:J6)</f>
-        <v>5.3266533066132258</v>
+        <v>5.3460721868365173</v>
       </c>
       <c r="J10" s="17"/>
     </row>
     <row r="11" spans="1:10" s="14" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="C11" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D11" s="16">
         <f>SQRT(SUM(D7:J7)/(B6-1))</f>
-        <v>1.5904809147565737</v>
+        <v>1.5795166467407569</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="14" customFormat="1" ht="65.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
+      <c r="A12" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
       <c r="D12" s="18">
         <f>SUM(H6:J6)</f>
-        <v>0.67735470941883769</v>
+        <v>0.67940552016985145</v>
       </c>
     </row>
   </sheetData>
@@ -13142,7 +13139,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -13167,17 +13164,17 @@
         <v>56</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -13208,141 +13205,141 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5">
         <f>SUM(C5:J5)</f>
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="C5">
-        <f>SUM('Collapsed Data'!AC2:AC13)</f>
+        <f>SUM('Collapsed Data'!AC3:AC13)</f>
         <v>18</v>
       </c>
       <c r="D5">
-        <f>SUM('Collapsed Data'!AD2:AD13)</f>
-        <v>14</v>
+        <f>SUM('Collapsed Data'!AD3:AD13)</f>
+        <v>13</v>
       </c>
       <c r="E5">
-        <f>SUM('Collapsed Data'!AE2:AE13)</f>
-        <v>20</v>
+        <f>SUM('Collapsed Data'!AE3:AE13)</f>
+        <v>18</v>
       </c>
       <c r="F5">
-        <f>SUM('Collapsed Data'!AF2:AF13)</f>
-        <v>22</v>
+        <f>SUM('Collapsed Data'!AF3:AF13)</f>
+        <v>19</v>
       </c>
       <c r="G5">
-        <f>SUM('Collapsed Data'!AG2:AG13)</f>
-        <v>114</v>
+        <f>SUM('Collapsed Data'!AG3:AG13)</f>
+        <v>110</v>
       </c>
       <c r="H5">
-        <f>SUM('Collapsed Data'!AH2:AH13)</f>
-        <v>72</v>
+        <f>SUM('Collapsed Data'!AH3:AH13)</f>
+        <v>67</v>
       </c>
       <c r="I5">
-        <f>SUM('Collapsed Data'!AI2:AI13)</f>
-        <v>100</v>
+        <f>SUM('Collapsed Data'!AI3:AI13)</f>
+        <v>94</v>
       </c>
       <c r="J5">
-        <f>SUM('Collapsed Data'!AJ2:AJ13)</f>
-        <v>152</v>
+        <f>SUM('Collapsed Data'!AJ3:AJ13)</f>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
-        <v>69</v>
+      <c r="A6" s="24" t="s">
+        <v>68</v>
       </c>
       <c r="B6" s="10">
         <f>B5-C5</f>
-        <v>494</v>
+        <v>466</v>
       </c>
       <c r="D6" s="9">
         <f t="shared" ref="D6:J6" si="0">D5/$B$6</f>
-        <v>2.8340080971659919E-2</v>
+        <v>2.7896995708154508E-2</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>4.048582995951417E-2</v>
+        <v>3.8626609442060089E-2</v>
       </c>
       <c r="F6" s="9">
         <f t="shared" si="0"/>
-        <v>4.4534412955465584E-2</v>
+        <v>4.07725321888412E-2</v>
       </c>
       <c r="G6" s="9">
         <f t="shared" si="0"/>
-        <v>0.23076923076923078</v>
+        <v>0.23605150214592274</v>
       </c>
       <c r="H6" s="9">
         <f t="shared" si="0"/>
-        <v>0.145748987854251</v>
+        <v>0.14377682403433475</v>
       </c>
       <c r="I6" s="9">
         <f t="shared" si="0"/>
-        <v>0.20242914979757085</v>
+        <v>0.20171673819742489</v>
       </c>
       <c r="J6" s="9">
         <f t="shared" si="0"/>
-        <v>0.30769230769230771</v>
+        <v>0.31115879828326182</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="20"/>
+      <c r="A7" s="22"/>
       <c r="D7" s="13">
         <f>D5*(D4-$D$10)^2</f>
-        <v>254.44321329639897</v>
+        <v>238.02459061688367</v>
       </c>
       <c r="E7" s="13">
         <f t="shared" ref="E7:J7" si="1">E5*(E4-$D$10)^2</f>
-        <v>212.96398891966763</v>
+        <v>193.52959162998025</v>
       </c>
       <c r="F7" s="13">
         <f t="shared" si="1"/>
-        <v>112.68144044321333</v>
+        <v>98.680377240324901</v>
       </c>
       <c r="G7" s="13">
         <f t="shared" si="1"/>
-        <v>181.89473684210537</v>
+        <v>179.93405662288851</v>
       </c>
       <c r="H7" s="13">
         <f t="shared" si="1"/>
-        <v>4.9861495844875492</v>
+        <v>5.2142238759232855</v>
       </c>
       <c r="I7" s="13">
         <f t="shared" si="1"/>
-        <v>54.293628808864213</v>
+        <v>48.869126342353013</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="1"/>
-        <v>458.52631578947347</v>
+        <v>429.4819392510455</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="14" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="C10" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10" s="16">
         <f>SUMPRODUCT(D4:J4,D6:J6)</f>
-        <v>5.2631578947368425</v>
+        <v>5.2789699570815447</v>
       </c>
       <c r="J10" s="17"/>
     </row>
     <row r="11" spans="1:10" s="14" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="C11" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D11" s="16">
         <f>SQRT(SUM(D7:J7)/(B6-1))</f>
-        <v>1.611186473787199</v>
+        <v>1.6022389613968517</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="14" customFormat="1" ht="65.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
+      <c r="A12" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
       <c r="D12" s="18">
         <f>SUM(H6:J6)</f>
-        <v>0.65587044534412953</v>
+        <v>0.6566523605150214</v>
       </c>
     </row>
   </sheetData>
@@ -13367,7 +13364,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -13392,17 +13389,17 @@
         <v>56</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -13433,141 +13430,141 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5">
         <f>SUM(C5:J5)</f>
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="C5">
-        <f>SUM('Collapsed Data'!AK2:AK13)</f>
+        <f>SUM('Collapsed Data'!AK3:AK13)</f>
         <v>19</v>
       </c>
       <c r="D5">
-        <f>SUM('Collapsed Data'!AL2:AL13)</f>
+        <f>SUM('Collapsed Data'!AL3:AL13)</f>
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <f>SUM('Collapsed Data'!AM3:AM13)</f>
         <v>11</v>
       </c>
-      <c r="E5">
-        <f>SUM('Collapsed Data'!AM2:AM13)</f>
-        <v>13</v>
-      </c>
       <c r="F5">
-        <f>SUM('Collapsed Data'!AN2:AN13)</f>
-        <v>19</v>
+        <f>SUM('Collapsed Data'!AN3:AN13)</f>
+        <v>16</v>
       </c>
       <c r="G5">
-        <f>SUM('Collapsed Data'!AO2:AO13)</f>
-        <v>85</v>
+        <f>SUM('Collapsed Data'!AO3:AO13)</f>
+        <v>81</v>
       </c>
       <c r="H5">
-        <f>SUM('Collapsed Data'!AP2:AP13)</f>
-        <v>72</v>
+        <f>SUM('Collapsed Data'!AP3:AP13)</f>
+        <v>67</v>
       </c>
       <c r="I5">
-        <f>SUM('Collapsed Data'!AQ2:AQ13)</f>
-        <v>92</v>
+        <f>SUM('Collapsed Data'!AQ3:AQ13)</f>
+        <v>86</v>
       </c>
       <c r="J5">
-        <f>SUM('Collapsed Data'!AR2:AR13)</f>
-        <v>201</v>
+        <f>SUM('Collapsed Data'!AR3:AR13)</f>
+        <v>194</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
-        <v>69</v>
+      <c r="A6" s="24" t="s">
+        <v>68</v>
       </c>
       <c r="B6" s="10">
         <f>B5-C5</f>
-        <v>493</v>
+        <v>465</v>
       </c>
       <c r="D6" s="9">
         <f t="shared" ref="D6:J6" si="0">D5/$B$6</f>
-        <v>2.231237322515213E-2</v>
+        <v>2.1505376344086023E-2</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>2.6369168356997971E-2</v>
+        <v>2.3655913978494623E-2</v>
       </c>
       <c r="F6" s="9">
         <f t="shared" si="0"/>
-        <v>3.8539553752535496E-2</v>
+        <v>3.4408602150537634E-2</v>
       </c>
       <c r="G6" s="9">
         <f t="shared" si="0"/>
-        <v>0.17241379310344829</v>
+        <v>0.17419354838709677</v>
       </c>
       <c r="H6" s="9">
         <f t="shared" si="0"/>
-        <v>0.1460446247464503</v>
+        <v>0.14408602150537633</v>
       </c>
       <c r="I6" s="9">
         <f t="shared" si="0"/>
-        <v>0.18661257606490872</v>
+        <v>0.18494623655913978</v>
       </c>
       <c r="J6" s="9">
         <f t="shared" si="0"/>
-        <v>0.40770791075050711</v>
+        <v>0.41720430107526879</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="20"/>
+      <c r="A7" s="22"/>
       <c r="D7" s="13">
         <f>D5*(D4-$D$10)^2</f>
-        <v>231.16161761620089</v>
+        <v>213.38439125910509</v>
       </c>
       <c r="E7" s="13">
         <f t="shared" ref="E7:J7" si="1">E5*(E4-$D$10)^2</f>
-        <v>167.00236166369749</v>
+        <v>144.09702393340268</v>
       </c>
       <c r="F7" s="13">
         <f t="shared" si="1"/>
-        <v>126.88159177778971</v>
+        <v>109.77631633714878</v>
       </c>
       <c r="G7" s="13">
         <f t="shared" si="1"/>
-        <v>213.31782891515715</v>
+        <v>212.40711758584803</v>
       </c>
       <c r="H7" s="13">
         <f t="shared" si="1"/>
-        <v>24.57104534476591</v>
+        <v>25.701227887617048</v>
       </c>
       <c r="I7" s="13">
         <f t="shared" si="1"/>
-        <v>15.907491904924488</v>
+        <v>12.460603537981283</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="1"/>
-        <v>402.91465506955365</v>
+        <v>369.79912591050999</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="14" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="C10" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10" s="16">
         <f>SUMPRODUCT(D4:J4,D6:J6)</f>
-        <v>5.5841784989858017</v>
+        <v>5.6193548387096772</v>
       </c>
       <c r="J10" s="17"/>
     </row>
     <row r="11" spans="1:10" s="14" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="C11" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D11" s="16">
         <f>SQRT(SUM(D7:J7)/(B6-1))</f>
-        <v>1.5498207293995665</v>
+        <v>1.5310196388662012</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="14" customFormat="1" ht="65.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
+      <c r="A12" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
       <c r="D12" s="18">
         <f>SUM(H6:J6)</f>
-        <v>0.74036511156186613</v>
+        <v>0.74623655913978482</v>
       </c>
     </row>
   </sheetData>
@@ -13592,7 +13589,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -13617,17 +13614,17 @@
         <v>56</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -13658,141 +13655,141 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5">
         <f>SUM(C5:J5)</f>
-        <v>510</v>
+        <v>482</v>
       </c>
       <c r="C5">
-        <f>SUM('Collapsed Data'!AS2:AS13)</f>
+        <f>SUM('Collapsed Data'!AS3:AS13)</f>
         <v>21</v>
       </c>
       <c r="D5">
-        <f>SUM('Collapsed Data'!AT2:AT13)</f>
-        <v>15</v>
+        <f>SUM('Collapsed Data'!AT3:AT13)</f>
+        <v>14</v>
       </c>
       <c r="E5">
-        <f>SUM('Collapsed Data'!AU2:AU13)</f>
-        <v>20</v>
+        <f>SUM('Collapsed Data'!AU3:AU13)</f>
+        <v>18</v>
       </c>
       <c r="F5">
-        <f>SUM('Collapsed Data'!AV2:AV13)</f>
-        <v>31</v>
+        <f>SUM('Collapsed Data'!AV3:AV13)</f>
+        <v>28</v>
       </c>
       <c r="G5">
-        <f>SUM('Collapsed Data'!AW2:AW13)</f>
-        <v>93</v>
+        <f>SUM('Collapsed Data'!AW3:AW13)</f>
+        <v>89</v>
       </c>
       <c r="H5">
-        <f>SUM('Collapsed Data'!AX2:AX13)</f>
-        <v>75</v>
+        <f>SUM('Collapsed Data'!AX3:AX13)</f>
+        <v>70</v>
       </c>
       <c r="I5">
-        <f>SUM('Collapsed Data'!AY2:AY13)</f>
-        <v>91</v>
+        <f>SUM('Collapsed Data'!AY3:AY13)</f>
+        <v>85</v>
       </c>
       <c r="J5">
-        <f>SUM('Collapsed Data'!AZ2:AZ13)</f>
-        <v>164</v>
+        <f>SUM('Collapsed Data'!AZ3:AZ13)</f>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
-        <v>69</v>
+      <c r="A6" s="24" t="s">
+        <v>68</v>
       </c>
       <c r="B6" s="10">
         <f>B5-C5</f>
-        <v>489</v>
+        <v>461</v>
       </c>
       <c r="D6" s="9">
         <f t="shared" ref="D6:J6" si="0">D5/$B$6</f>
-        <v>3.0674846625766871E-2</v>
+        <v>3.0368763557483729E-2</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>4.0899795501022497E-2</v>
+        <v>3.9045553145336226E-2</v>
       </c>
       <c r="F6" s="9">
         <f t="shared" si="0"/>
-        <v>6.3394683026584867E-2</v>
+        <v>6.0737527114967459E-2</v>
       </c>
       <c r="G6" s="9">
         <f t="shared" si="0"/>
-        <v>0.19018404907975461</v>
+        <v>0.19305856832971802</v>
       </c>
       <c r="H6" s="9">
         <f t="shared" si="0"/>
-        <v>0.15337423312883436</v>
+        <v>0.15184381778741865</v>
       </c>
       <c r="I6" s="9">
         <f t="shared" si="0"/>
-        <v>0.18609406952965235</v>
+        <v>0.18438177874186551</v>
       </c>
       <c r="J6" s="9">
         <f t="shared" si="0"/>
-        <v>0.33537832310838445</v>
+        <v>0.34056399132321041</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="20"/>
+      <c r="A7" s="22"/>
       <c r="D7" s="13">
         <f>D5*(D4-$D$10)^2</f>
-        <v>276.63818736121044</v>
+        <v>260.35081709572228</v>
       </c>
       <c r="E7" s="13">
         <f t="shared" ref="E7:J7" si="1">E5*(E4-$D$10)^2</f>
-        <v>217.07177537731945</v>
+        <v>197.49164553150038</v>
       </c>
       <c r="F7" s="13">
         <f t="shared" si="1"/>
-        <v>163.20358312318868</v>
+        <v>149.71681857322332</v>
       </c>
       <c r="G7" s="13">
         <f t="shared" si="1"/>
-        <v>155.83774323459673</v>
+        <v>153.2847342145011</v>
       </c>
       <c r="H7" s="13">
         <f t="shared" si="1"/>
-        <v>6.5038202416349913</v>
+        <v>6.8300073875052254</v>
       </c>
       <c r="I7" s="13">
         <f t="shared" si="1"/>
-        <v>45.296209868643899</v>
+        <v>40.191628121456262</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="1"/>
-        <v>477.04377281794564</v>
+        <v>447.15387185266405</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="14" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="C10" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10" s="16">
         <f>SUMPRODUCT(D4:J4,D6:J6)</f>
-        <v>5.294478527607362</v>
+        <v>5.3123644251626896</v>
       </c>
       <c r="J10" s="17"/>
     </row>
     <row r="11" spans="1:10" s="14" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="C11" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D11" s="16">
         <f>SQRT(SUM(D7:J7)/(B6-1))</f>
-        <v>1.6580622034598371</v>
+        <v>1.6517576427502472</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="14" customFormat="1" ht="65.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
+      <c r="A12" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
       <c r="D12" s="18">
         <f>SUM(H6:J6)</f>
-        <v>0.67484662576687116</v>
+        <v>0.67678958785249455</v>
       </c>
     </row>
   </sheetData>
@@ -13817,7 +13814,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -13842,17 +13839,17 @@
         <v>56</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -13883,141 +13880,141 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5">
         <f>SUM(C5:J5)</f>
-        <v>508</v>
+        <v>480</v>
       </c>
       <c r="C5">
-        <f>SUM('Collapsed Data'!BA2:BA13)</f>
+        <f>SUM('Collapsed Data'!BA3:BA13)</f>
         <v>24</v>
       </c>
       <c r="D5">
-        <f>SUM('Collapsed Data'!BB2:BB13)</f>
-        <v>9</v>
+        <f>SUM('Collapsed Data'!BB3:BB13)</f>
+        <v>8</v>
       </c>
       <c r="E5">
-        <f>SUM('Collapsed Data'!BC2:BC13)</f>
-        <v>9</v>
+        <f>SUM('Collapsed Data'!BC3:BC13)</f>
+        <v>7</v>
       </c>
       <c r="F5">
-        <f>SUM('Collapsed Data'!BD2:BD13)</f>
-        <v>14</v>
+        <f>SUM('Collapsed Data'!BD3:BD13)</f>
+        <v>11</v>
       </c>
       <c r="G5">
-        <f>SUM('Collapsed Data'!BE2:BE13)</f>
-        <v>87</v>
+        <f>SUM('Collapsed Data'!BE3:BE13)</f>
+        <v>83</v>
       </c>
       <c r="H5">
-        <f>SUM('Collapsed Data'!BF2:BF13)</f>
-        <v>56</v>
+        <f>SUM('Collapsed Data'!BF3:BF13)</f>
+        <v>51</v>
       </c>
       <c r="I5">
-        <f>SUM('Collapsed Data'!BG2:BG13)</f>
-        <v>91</v>
+        <f>SUM('Collapsed Data'!BG3:BG13)</f>
+        <v>85</v>
       </c>
       <c r="J5">
-        <f>SUM('Collapsed Data'!BH2:BH13)</f>
-        <v>218</v>
+        <f>SUM('Collapsed Data'!BH3:BH13)</f>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
-        <v>69</v>
+      <c r="A6" s="24" t="s">
+        <v>68</v>
       </c>
       <c r="B6" s="10">
         <f>B5-C5</f>
-        <v>484</v>
+        <v>456</v>
       </c>
       <c r="D6" s="9">
         <f t="shared" ref="D6:J6" si="0">D5/$B$6</f>
-        <v>1.859504132231405E-2</v>
+        <v>1.7543859649122806E-2</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="0"/>
-        <v>1.859504132231405E-2</v>
+        <v>1.5350877192982455E-2</v>
       </c>
       <c r="F6" s="9">
         <f t="shared" si="0"/>
-        <v>2.8925619834710745E-2</v>
+        <v>2.4122807017543858E-2</v>
       </c>
       <c r="G6" s="9">
         <f t="shared" si="0"/>
-        <v>0.17975206611570249</v>
+        <v>0.18201754385964913</v>
       </c>
       <c r="H6" s="9">
         <f t="shared" si="0"/>
-        <v>0.11570247933884298</v>
+        <v>0.1118421052631579</v>
       </c>
       <c r="I6" s="9">
         <f t="shared" si="0"/>
-        <v>0.18801652892561985</v>
+        <v>0.18640350877192982</v>
       </c>
       <c r="J6" s="9">
         <f t="shared" si="0"/>
-        <v>0.45041322314049587</v>
+        <v>0.46271929824561403</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="20"/>
+      <c r="A7" s="22"/>
       <c r="D7" s="13">
         <f>D5*(D4-$D$10)^2</f>
-        <v>200.59688972747765</v>
+        <v>181.66855186211146</v>
       </c>
       <c r="E7" s="13">
         <f t="shared" ref="E7:J7" si="1">E5*(E4-$D$10)^2</f>
-        <v>124.61755088450242</v>
+        <v>99.245070598645768</v>
       </c>
       <c r="F7" s="13">
         <f t="shared" si="1"/>
-        <v>103.65944095348679</v>
+        <v>84.118820213912002</v>
       </c>
       <c r="G7" s="13">
         <f t="shared" si="1"/>
-        <v>257.70244091933608</v>
+        <v>258.66648872730087</v>
       </c>
       <c r="H7" s="13">
         <f t="shared" si="1"/>
-        <v>29.117102656922338</v>
+        <v>29.873860226223488</v>
       </c>
       <c r="I7" s="13">
         <f t="shared" si="1"/>
-        <v>7.0797546274161611</v>
+        <v>4.6801179208987209</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="1"/>
-        <v>356.5718615531726</v>
+        <v>321.63963431055686</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="14" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="C10" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10" s="16">
         <f>SUMPRODUCT(D4:J4,D6:J6)</f>
-        <v>5.7210743801652892</v>
+        <v>5.7653508771929829</v>
       </c>
       <c r="J10" s="17"/>
     </row>
     <row r="11" spans="1:10" s="14" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="C11" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D11" s="16">
         <f>SQRT(SUM(D7:J7)/(B6-1))</f>
-        <v>1.4948808723819724</v>
+        <v>1.4675183087460011</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="14" customFormat="1" ht="65.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
+      <c r="A12" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
       <c r="D12" s="18">
         <f>SUM(H6:J6)</f>
-        <v>0.75413223140495877</v>
+        <v>0.76096491228070173</v>
       </c>
     </row>
   </sheetData>
